--- a/nurse_forms/021_patient_screening_questionnaire--nurse_forms.xlsx
+++ b/nurse_forms/021_patient_screening_questionnaire--nurse_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,8 +442,8 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>patient_info</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the patient's name?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter the patient's name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,87 +547,103 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>medical_history</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the patient's contact info?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter the patient's address</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Is the patient taking any medications?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Yes or No</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>medical_info</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is the patient's medical history?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Describe the patient's medical history</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>medical_history_additional_info</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>allergies</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Additional medical history info?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter any additional details</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,38 +655,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medications</t>
+          <t>medical_history_info</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>medications</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What are the patient's medical history info?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter any medical history information</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_history_details</t>
+          <t>contact_preferences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>medical_history_details</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Is the patient's contact info public?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Yes or No</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_preferences</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>contact_preferences</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Who is the patient's emergency contact?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter the emergency contact name</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>emergency_contact</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>emergency_contact</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is the patient's age?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0-100 years</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>medical_info</t>
+          <t>medical_conditions_info</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>medical_info</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is the patient's medical conditions info?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter any medical conditions information</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>medical_history_info</t>
+          <t>medical_conditions_additional_info</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>medical_history_info</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Additional medical conditions info?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter any additional medical conditions information</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>medical_history_additional_info</t>
+          <t>medical_info_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>medical_history_additional_info</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is the patient's medical info?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter any medical info</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>medical_info_additional_info</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Additional medical info?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Enter any additional medical info</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,23 +866,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>allergies_additional_info</t>
+          <t>contact_preferences_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>allergies_additional_info</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What are the patient's contact preferences?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Check your options</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medical_conditions_additional_info</t>
+          <t>contact_preferences_info</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>medical_conditions_additional_info</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Contact preferences info?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Enter any contact preferences information</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,20 +920,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>medical_info_additional_info</t>
+          <t>medical_conditions_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>medical_info_additional_info</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>What are the patient's medical conditions?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>medications_additional_info</t>
+          <t>medical_history_info_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>medications_additional_info</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Medical history info?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Enter any medical history information</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,15 +979,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>medical_conditions_additional</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Medical conditions additional info?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Enter any medical conditions additional information</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -929,23 +1001,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>medical_conditions_info</t>
+          <t>age_range</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>medical_history_info</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>What is the patient's age range?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Enter 0-17, 18-64, 65-100</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -957,15 +1033,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>contact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>contact</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>What is the patient's contact info (again)?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Enter the patient's address</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
@@ -983,12 +1063,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1096,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1033,80 +1113,199 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>contact_preferences_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>contact_preferences_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>contact_preferences_choices</t>
+          <t>contact_preferences_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>contact_preferences_choices</t>
+          <t>contact_preferences_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>medical_conditions_2_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>medical_conditions_2_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>medical_conditions_2_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>age_range_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0-1_year</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0-1 year</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>age_range_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2-17_years</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2-17 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>age_range_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>18-64_years</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>18-64 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>age_range_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>65-100_years</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>65-100 years</t>
         </is>
       </c>
     </row>
